--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/35bf8124-cfc0-4314-a1b3-c251ad1eb605.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$2:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notes'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$2:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notes'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Limited</t>
+          <t>Agricultural Development Bank Limited</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Limited</t>
+          <t>Citizens Bank International Limited</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Green Development Bank Limited</t>
+          <t>Everest Bank Limited</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -714,57 +714,1565 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Global IME Bank Limited</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Himalayan Bank Limited</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Bank Limited</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Sunrise Bank Limited</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Machhapuchchhre Bank Limited</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Nabil Bank Limited published a notice regarding the new interest rate on deposits and loans which</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Bank Limited</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Limited</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Limited</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NIC Asia Bank Limited</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>NMB Bank Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Limited</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Limited</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanima Bank Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Corporate Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Garima Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Green Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Kamana Sewa Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Lumbini Bikash Bank Limited</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Narayani Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Salapa Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Shine Resunga Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sindu Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J6"/>
+  <autoFilter ref="A2:J35"/>
   <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:C1"/>
@@ -780,10 +2288,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
@@ -826,7 +2334,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Limited</t>
+          <t>Agricultural Development Bank Limited</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -841,7 +2349,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66406</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66416</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -858,7 +2366,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Limited</t>
+          <t>Citizens Bank International Limited</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -873,7 +2381,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66396</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66415</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -890,7 +2398,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Green Development Bank Limited</t>
+          <t>Everest Bank Limited</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -905,7 +2413,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66395</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66414</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -922,37 +2430,965 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Global IME Bank Limited</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66413</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Himalayan Bank Limited</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66412</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Kumari Bank Limited</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66411</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Laxmi Sunrise Bank Limited</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66410</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Machhapuchchhre Bank Limited</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66409</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Nabil Bank Limited published a notice regarding the new interest rate on deposits and loans which</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66408</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nepal Bank Limited</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66407</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Limited</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66406</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Limited</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66417</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>NIC Asia Bank Limited</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66405</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>NMB Bank Limited</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66404</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66402</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Limited</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66403</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66401</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-07-16 | Rastriya Banijya Bank Limited has published a notice regarding new interest rate on loan which is going to be effective from Shrawan 01, 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Sanima Bank Limited</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66399</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66398</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66397</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66418</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Garima Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66396</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Green Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66395</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66394</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Kamana Sewa Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66393</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>Lumbini Bikash Bank Limited</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=66392</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66391</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66390</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Narayani Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66389</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Salapa Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66388</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66387</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Shine Resunga Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66386</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Sindu Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66385</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2920,12 +2920,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66398</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=4104</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-07-16 | Siddhartha Bank Limited has published a notice regarding the new interest rate on deposits, loans and advances which is going to be effective from Shrawan 01, 2083</t>
         </is>
       </c>
     </row>

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2354,7 +2354,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/dbd6dc5b-3d51-40e3-92d8-2d4f2ff1f145.gif</t>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66385</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66570</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-07-16 | Sindu Bikas Bank Limited has published a notice regarding new interest rate on fixed deposit which is going to be effective from Shrawan 01, 2083</t>
         </is>
       </c>
     </row>

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$2:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notes'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$2:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notes'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -558,57 +558,109 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>Green Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Salapa Bikas Bank Limited</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J3"/>
+  <autoFilter ref="A2:J4"/>
   <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:C1"/>
@@ -624,10 +676,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
@@ -670,37 +722,69 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Green Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67049</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>Salapa Bikas Bank Limited</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67039</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$2:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notes'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$2:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notes'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Green Development Bank Limited</t>
+          <t>Agricultural Development Bank Limited</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -610,57 +610,1669 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Citizens Bank International Limited</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Everest Bank Limited</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Global IME Bank Limited</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Himalayan Bank Limited</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Bank Limited</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Sunrise Bank Limited</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Machhapuchchhre Bank Limited</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Nabil Bank Limited published a notice regarding the new interest rate on deposits and loans which</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Bank Limited</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Limited</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Limited</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NIC Asia Bank Limited</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>NMB Bank Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Limited</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Limited</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanima Bank Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Corporate Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Garima Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Green Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Kamana Sewa Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Lumbini Bikash Bank Limited</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Narayani Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>Salapa Bikas Bank Limited</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Shine Resunga Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sindu Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J4"/>
+  <autoFilter ref="A2:J35"/>
   <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:C1"/>
@@ -676,10 +2288,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
@@ -722,7 +2334,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Green Development Bank Limited</t>
+          <t>Agricultural Development Bank Limited</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -732,12 +2344,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67049</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66818</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -754,37 +2366,1029 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>Citizens Bank International Limited</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66817</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Everest Bank Limited</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66816</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Global IME Bank Limited</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66815</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Himalayan Bank Limited</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66814</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Kumari Bank Limited</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66813</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Laxmi Sunrise Bank Limited</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66812</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Machhapuchchhre Bank Limited</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66811</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Nabil Bank Limited published a notice regarding the new interest rate on deposits and loans which</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66810</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nepal Bank Limited</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66809</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Limited</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66808</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Limited</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66807</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>NIC Asia Bank Limited</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66806</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>NMB Bank Limited</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66805</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66803</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Limited</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66804</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66802</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-08-16 | Rastriya Banijya Bank Limited has published a notice regarding new interest rate on loan which is going to be effective from Bhadra 01, 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Sanima Bank Limited</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66800</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66799</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66798</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66797</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Garima Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66796</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Green Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67049</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66794</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Kamana Sewa Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66793</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Lumbini Bikash Bank Limited</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66792</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66791</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66790</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Narayani Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66789</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Salapa Bikas Bank Limited</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67039</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66787</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Shine Resunga Development Bank Limited</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66786</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Sindu Bikas Bank Limited</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66785</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Source document could not be read; all rates marked Not specified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>